--- a/output/roomself_excel/13654.xlsx
+++ b/output/roomself_excel/13654.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>87706</v>
+        <v>118647</v>
       </c>
       <c r="D2" t="n">
-        <v>2780</v>
+        <v>2760</v>
       </c>
       <c r="E2" t="n">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="F2" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>108836</v>
+        <v>162489</v>
       </c>
       <c r="D3" t="n">
-        <v>2652</v>
+        <v>3260</v>
       </c>
       <c r="E3" t="n">
-        <v>299</v>
+        <v>399</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4">
@@ -514,13 +514,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>150448</v>
+        <v>108836</v>
       </c>
       <c r="D4" t="n">
-        <v>3524</v>
+        <v>2652</v>
       </c>
       <c r="E4" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F4" t="n">
         <v>33</v>
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24885</v>
+        <v>119602</v>
       </c>
       <c r="D5" t="n">
-        <v>1296</v>
+        <v>2888</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>367438</v>
+        <v>87706</v>
       </c>
       <c r="D6" t="n">
-        <v>7268</v>
+        <v>2780</v>
       </c>
       <c r="E6" t="n">
-        <v>1099</v>
+        <v>397</v>
       </c>
       <c r="F6" t="n">
-        <v>969</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7">
@@ -576,17 +576,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14280</v>
+        <v>15232</v>
       </c>
       <c r="D7" t="n">
-        <v>964</v>
+        <v>992</v>
       </c>
       <c r="E7" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F7" t="n">
         <v>31</v>
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15232</v>
+        <v>14280</v>
       </c>
       <c r="D8" t="n">
-        <v>992</v>
+        <v>964</v>
       </c>
       <c r="E8" t="n">
-        <v>335</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>112</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,82 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>30846</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1412</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>60918</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>1996</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>314</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>225</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>24885</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1296</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>86302</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2488</v>
+      </c>
+      <c r="E12" t="n">
+        <v>177</v>
+      </c>
+      <c r="F12" t="n">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/13654.xlsx
+++ b/output/roomself_excel/13654.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,34 @@
       <c r="D2" t="n">
         <v>2760</v>
       </c>
-      <c r="E2" t="n">
-        <v>389</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>355</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="G2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>331</v>
+      </c>
+      <c r="J2" t="n">
+        <v>31</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +569,42 @@
       <c r="D3" t="n">
         <v>3260</v>
       </c>
-      <c r="E3" t="n">
-        <v>399</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>304</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>273</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>366</v>
+      </c>
+      <c r="M3" t="n">
+        <v>31</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +621,26 @@
       <c r="D4" t="n">
         <v>2652</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>299</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>33</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +657,34 @@
       <c r="D5" t="n">
         <v>2888</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>295</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>33</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>427</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +701,34 @@
       <c r="D6" t="n">
         <v>2780</v>
       </c>
-      <c r="E6" t="n">
-        <v>397</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>354</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="G6" t="n">
+        <v>33</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>364</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +745,26 @@
       <c r="D7" t="n">
         <v>992</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>91</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>31</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +781,26 @@
       <c r="D8" t="n">
         <v>964</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>105</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>31</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +817,26 @@
       <c r="D9" t="n">
         <v>1412</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +853,49 @@
       <c r="D10" t="n">
         <v>1996</v>
       </c>
-      <c r="E10" t="n">
-        <v>314</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>225</v>
+        <v>213</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>285</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>213</v>
+      </c>
+      <c r="M10" t="n">
+        <v>16</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>286</v>
+      </c>
+      <c r="P10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -673,12 +913,18 @@
       <c r="D11" t="n">
         <v>1296</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +941,18 @@
       <c r="D12" t="n">
         <v>2488</v>
       </c>
-      <c r="E12" t="n">
-        <v>177</v>
-      </c>
-      <c r="F12" t="n">
-        <v>124</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/13654.xlsx
+++ b/output/roomself_excel/13654.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,46 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
         </is>
       </c>
     </row>
@@ -553,6 +593,26 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>157</v>
+      </c>
+      <c r="T2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -605,6 +665,38 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>157</v>
+      </c>
+      <c r="T3" t="n">
+        <v>33</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>260</v>
+      </c>
+      <c r="X3" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -641,6 +733,26 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>156</v>
+      </c>
+      <c r="T4" t="n">
+        <v>33</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -685,6 +797,26 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>157</v>
+      </c>
+      <c r="T5" t="n">
+        <v>33</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -729,6 +861,26 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>85</v>
+      </c>
+      <c r="T6" t="n">
+        <v>33</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -765,6 +917,26 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>64</v>
+      </c>
+      <c r="T7" t="n">
+        <v>31</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -801,6 +973,26 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>92</v>
+      </c>
+      <c r="T8" t="n">
+        <v>31</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -837,6 +1029,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -897,6 +1097,26 @@
       <c r="P10" t="n">
         <v>11</v>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>92</v>
+      </c>
+      <c r="T10" t="n">
+        <v>12</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -925,6 +1145,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -953,6 +1181,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
